--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ExportExcelTemplates/ReportPTEventSchool.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ExportExcelTemplates/ReportPTEventSchool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ExportExcelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2886CED5-BE8F-4CEF-BE2B-D952D24FB019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E4ED67-BB61-4D72-A665-9F1FED90ADE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6AC1E1EF-49BA-41A1-86FC-9BA1D743D91D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>TEMPLATE BÁO CÁO SỰ KIỆN SỞ HN</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Đã hoàn thành PT</t>
   </si>
   <si>
-    <t>Hoàn thành PT/Đăng ký TK</t>
-  </si>
-  <si>
     <t>(Thể hiện năng lực của học viên sẵn sàng bắt đầu khóa học)</t>
   </si>
   <si>
@@ -82,6 +79,12 @@
   </si>
   <si>
     <t>[{0}][{1}] SỐ LIỆU ĐĂNG KÝ &amp; KẾT QUẢ ĐÁNH GIÁ NĂNG LỰC ĐẦU VÀO TIẾNG ANH TRÊN HỆ THỐNG - PLACEMENT TEST (PT)</t>
+  </si>
+  <si>
+    <t>xác thực thành công</t>
+  </si>
+  <si>
+    <t>Hoàn thành PT/xác thực thành công</t>
   </si>
 </sst>
 </file>
@@ -313,6 +316,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -322,41 +337,29 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -672,10 +675,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199BB52E-5532-497C-A094-C2B96063CF16}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -695,8 +701,10 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
@@ -714,8 +722,10 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -735,8 +745,10 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
@@ -754,136 +766,154 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="12"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="17"/>
     </row>
-    <row r="7" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="G7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="20"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="17"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20" t="s">
+      <c r="I8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="J8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="K8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="20" t="s">
+      <c r="M8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="L8" s="20" t="s">
+      <c r="O8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="N8" s="20" t="s">
+      <c r="Q8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q8" s="20" t="s">
-        <v>11</v>
+      <c r="S8" s="9" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A5:S5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="F6:Q6"/>
-    <mergeCell ref="F7:Q7"/>
+    <mergeCell ref="H6:S6"/>
+    <mergeCell ref="H7:S7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ExportExcelTemplates/ReportPTEventSchool.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ExportExcelTemplates/ReportPTEventSchool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ExportExcelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E4ED67-BB61-4D72-A665-9F1FED90ADE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2749EB4F-3133-45F5-93D3-EC20ACB12171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6AC1E1EF-49BA-41A1-86FC-9BA1D743D91D}"/>
+    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{6AC1E1EF-49BA-41A1-86FC-9BA1D743D91D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>TEMPLATE BÁO CÁO SỰ KIỆN SỞ HN</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Hoàn thành PT/xác thực thành công</t>
+  </si>
+  <si>
+    <t>Đang làm bài PT</t>
   </si>
 </sst>
 </file>
@@ -675,13 +678,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199BB52E-5532-497C-A094-C2B96063CF16}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,8 +706,9 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
@@ -724,8 +728,9 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -747,8 +752,9 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
@@ -768,8 +774,9 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>17</v>
       </c>
@@ -791,8 +798,9 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
@@ -812,12 +820,14 @@
         <v>3</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="I6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="16"/>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
       <c r="L6" s="16"/>
@@ -827,9 +837,10 @@
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
-      <c r="S6" s="17"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="17"/>
     </row>
-    <row r="7" spans="1:19" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="7" t="s">
@@ -842,15 +853,17 @@
         <v>18</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="I7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="19"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
@@ -860,9 +873,10 @@
       <c r="P7" s="19"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
-      <c r="S7" s="20"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="20"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="8"/>
@@ -870,50 +884,51 @@
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="J8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="S8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A5:S5"/>
+    <mergeCell ref="A5:T5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="H6:S6"/>
-    <mergeCell ref="H7:S7"/>
+    <mergeCell ref="I6:T6"/>
+    <mergeCell ref="I7:T7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
